--- a/output/pdf_financials_xlsx/RYE.xlsx
+++ b/output/pdf_financials_xlsx/RYE.xlsx
@@ -1232,7 +1232,7 @@
         <v>-0.058632</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>3.872456</v>
+        <v>-3.872456</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-20.992978</v>
@@ -1492,7 +1492,7 @@
         <v>-0.058632</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>3.872456</v>
+        <v>-3.872456</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-20.992978</v>
@@ -1647,7 +1647,7 @@
         <v>-0.058632</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.872456</v>
+        <v>-3.872456</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-20.992978</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>96.81140000000001</v>
+        <v>-96.81140000000001</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>116.657405</v>
@@ -1869,7 +1869,7 @@
         <v>-0.058632</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>3.872456</v>
+        <v>-3.872456</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-20.992978</v>
@@ -1975,7 +1975,7 @@
         <v>-0.058632</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3.872456</v>
+        <v>-3.872456</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-20.992978</v>
@@ -2105,7 +2105,7 @@
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -29517,10 +29517,10 @@
         </is>
       </c>
       <c r="N260" s="5" t="n">
-        <v>3.872456</v>
+        <v>-3.872456</v>
       </c>
       <c r="O260" s="5" t="n">
-        <v>20.992978</v>
+        <v>-20.992978</v>
       </c>
       <c r="P260" t="inlineStr">
         <is>
@@ -29605,10 +29605,10 @@
         </is>
       </c>
       <c r="N261" s="5" t="n">
-        <v>3.872456</v>
+        <v>-3.872456</v>
       </c>
       <c r="O261" s="5" t="n">
-        <v>20.591529</v>
+        <v>-20.591529</v>
       </c>
       <c r="P261" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RYE.xlsx
+++ b/output/pdf_financials_xlsx/RYE.xlsx
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.0065</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000248</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.010774</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1008,31 +1008,31 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002937</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015853</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.029561</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.034174</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008732</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.170376</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.284123</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.285064</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.20904</v>
       </c>
     </row>
     <row r="13">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.081626</v>
+        <v>-0.088126</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.126523</v>
+        <v>-0.126771</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.434451</v>
+        <v>-0.445225</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1857,31 +1857,31 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.124459</v>
+        <v>-0.121522</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.07617</v>
+        <v>-0.060317</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.084646</v>
+        <v>-0.055085</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.058632</v>
+        <v>-0.024458</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.872456</v>
+        <v>-3.863724</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-20.992978</v>
+        <v>-21.163354</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.360021</v>
+        <v>-0.644144</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.502199</v>
+        <v>0.217135</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.036388</v>
+        <v>-0.245428</v>
       </c>
     </row>
     <row r="28">
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.081626</v>
+        <v>-0.088126</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.126523</v>
+        <v>-0.126771</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.434451</v>
+        <v>-0.445225</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.124459</v>
+        <v>-0.121522</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.07617</v>
+        <v>-0.060317</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.084646</v>
+        <v>-0.055085</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.058632</v>
+        <v>-0.024458</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.872456</v>
+        <v>-3.863724</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-20.992978</v>
+        <v>-21.163354</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.360021</v>
+        <v>-0.644144</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.502199</v>
+        <v>0.217135</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.036388</v>
+        <v>-0.245428</v>
       </c>
     </row>
     <row r="30">
@@ -2211,31 +2211,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.450329</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.235851</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.728389</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.5572510000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.262787</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.546217</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.451233</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.641085</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.579446</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>19.060773</v>
@@ -2309,31 +2309,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.450329</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.235851</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.728389</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.5572510000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.262787</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.546217</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.451233</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.641085</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.579446</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>19.060773</v>
@@ -2897,31 +2897,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.450329</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.235851</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.154179</v>
+        <v>0.42579</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.56436</v>
+        <v>0.007109</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.262787</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.546217</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.451233</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.641085</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.579446</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.081446</v>
@@ -12066,7 +12066,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
@@ -24298,7 +24298,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -29042,7 +29042,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -31648,7 +31648,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E286" s="5" t="n">

--- a/output/pdf_financials_xlsx/RYE.xlsx
+++ b/output/pdf_financials_xlsx/RYE.xlsx
@@ -1922,19 +1922,19 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.003028</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.08568199999999999</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.049107</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.000793</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.000595</v>
       </c>
     </row>
     <row r="29">
@@ -1975,19 +1975,19 @@
         <v>-0.024458</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.863724</v>
+        <v>-3.860696</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-21.163354</v>
+        <v>-21.077672</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.644144</v>
+        <v>-0.595037</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.217135</v>
+        <v>0.217928</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.245428</v>
+        <v>-0.244833</v>
       </c>
     </row>
     <row r="30">
@@ -5554,19 +5554,19 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.003028</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.08568199999999999</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.049107</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.000793</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.000595</v>
       </c>
     </row>
     <row r="101">
@@ -15934,7 +15934,11 @@
           <t>Depreciation - property and equipment</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -16774,7 +16778,11 @@
           <t>Depreciation - right of use asset</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -19008,7 +19016,11 @@
           <t>Depreciation of property, plant and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -19092,7 +19104,11 @@
           <t>Depreciation of right of use asset (Note 7)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -23876,7 +23892,11 @@
           <t>Depreciation - property and equipment 5</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -25248,7 +25268,11 @@
           <t>Depreciation - right of use asset 6</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -28522,7 +28546,11 @@
           <t>Depreciation of property, plant and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -28606,7 +28634,11 @@
           <t>Depreciation of right of use asset (Note 7)</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RYE.xlsx
+++ b/output/pdf_financials_xlsx/RYE.xlsx
@@ -555,15 +555,11 @@
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -614,15 +610,11 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -667,15 +659,11 @@
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -726,15 +714,11 @@
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="3" t="n">
+        <v>0.00072</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.019717</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -779,15 +763,11 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -832,15 +812,11 @@
       <c r="D9" s="3" t="n">
         <v>0.037494</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="3" t="n">
+        <v>0.07943600000000001</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.04648</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0.018544</v>
@@ -885,15 +861,11 @@
       <c r="D10" s="3" t="n">
         <v>0.206022</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="3" t="n">
+        <v>0.08015600000000001</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.06619700000000001</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.018544</v>
@@ -938,15 +910,11 @@
       <c r="D11" s="3" t="n">
         <v>-0.445225</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="3" t="n">
+        <v>-0.08015600000000001</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-0.06619700000000001</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.018544</v>
@@ -997,15 +965,11 @@
       <c r="D12" s="3" t="n">
         <v>0.010774</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>-0.00583</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-0.001495</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>-0.002937</v>
@@ -1050,15 +1014,11 @@
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
@@ -1103,15 +1063,11 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -1156,15 +1112,11 @@
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="3" t="n">
+        <v>0.001224</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.000811</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0.00035</v>
@@ -1209,15 +1161,11 @@
       <c r="D16" s="3" t="n">
         <v>-0.434451</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="3" t="n">
+        <v>-0.360994</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.306166</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.124459</v>
@@ -1262,15 +1210,11 @@
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1469,15 +1413,11 @@
       <c r="D20" s="3" t="n">
         <v>-0.434451</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>-0.360994</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-0.306166</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.124459</v>
@@ -1522,15 +1462,11 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1575,15 +1511,11 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0</v>
@@ -1677,15 +1609,11 @@
       <c r="D24" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0</v>
@@ -1730,15 +1658,11 @@
       <c r="D25" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
@@ -1846,15 +1770,11 @@
       <c r="D27" s="3" t="n">
         <v>-0.445225</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="3" t="n">
+        <v>-0.355164</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-0.304671</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.121522</v>
@@ -1899,15 +1819,11 @@
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -1952,15 +1868,11 @@
       <c r="D29" s="3" t="n">
         <v>-0.445225</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="3" t="n">
+        <v>-0.355164</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-0.304671</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.121522</v>
@@ -2082,15 +1994,11 @@
       <c r="D31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -3751,16 +3659,16 @@
         <v>0</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.172289</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.024843</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.021189</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.017534</v>
       </c>
     </row>
     <row r="65">
@@ -3895,19 +3803,19 @@
         <v>0</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.054554</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>1.985894</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="68">
@@ -7337,7 +7245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R294"/>
+  <dimension ref="A1:R301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -29862,15 +29770,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H264" s="5" t="n">
+        <v>0.004142</v>
+      </c>
+      <c r="I264" s="5" t="n">
+        <v>0.005229</v>
       </c>
       <c r="J264" s="5" t="n">
         <v>0.039621</v>
@@ -29942,15 +29846,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H265" s="5" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="I265" s="5" t="n">
+        <v>0.048</v>
       </c>
       <c r="J265" s="5" t="n">
         <v>0.048</v>
@@ -30106,15 +30006,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H267" s="5" t="n">
+        <v>0.011274</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>0.013449</v>
       </c>
       <c r="J267" s="5" t="n">
         <v>0.014344</v>
@@ -30350,15 +30246,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H270" s="5" t="n">
+        <v>0.001224</v>
+      </c>
+      <c r="I270" s="5" t="n">
+        <v>0.000811</v>
       </c>
       <c r="J270" s="5" t="n">
         <v>0.00035</v>
@@ -30434,15 +30326,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H271" s="5" t="n">
+        <v>-0.00583</v>
+      </c>
+      <c r="I271" s="5" t="n">
+        <v>-0.001495</v>
       </c>
       <c r="J271" s="5" t="n">
         <v>-0.002937</v>
@@ -30518,15 +30406,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H272" s="5" t="n">
+        <v>0.356852</v>
+      </c>
+      <c r="I272" s="5" t="n">
+        <v>0.300937</v>
       </c>
       <c r="J272" s="5" t="n">
         <v>0.084838</v>
@@ -30602,15 +30486,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H273" s="5" t="n">
+        <v>-0.360994</v>
+      </c>
+      <c r="I273" s="5" t="n">
+        <v>-0.306166</v>
       </c>
       <c r="J273" s="5" t="n">
         <v>-0.124459</v>
@@ -30686,15 +30566,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H274" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I274" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="J274" s="5" t="n">
         <v>0</v>
@@ -30830,31 +30706,37 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>MINERAL PROPERTY EXPENDITURES (Note 5) $</t>
+          <t>Salaries</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
-      <c r="E276" s="5" t="n">
-        <v>0.000817</v>
-      </c>
-      <c r="F276" s="5" t="n">
-        <v>0.013095</v>
-      </c>
-      <c r="G276" s="5" t="n">
-        <v>0.239203</v>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H276" s="5" t="n">
+        <v>0.170912</v>
+      </c>
+      <c r="I276" s="5" t="n">
+        <v>0.09167500000000001</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -30910,33 +30792,37 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Office and sundry</t>
+          <t>Share-based compensation (Note 7)</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
-      <c r="E277" s="5" t="n">
-        <v>0.000382</v>
-      </c>
-      <c r="F277" s="5" t="n">
-        <v>0.001325</v>
-      </c>
-      <c r="G277" s="5" t="n">
-        <v>0.002703</v>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I277" s="5" t="n">
+        <v>0.051652</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30992,33 +30878,39 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Office facilities and administrative services</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" s="5" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="F278" s="5" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="G278" s="5" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" s="5" t="n">
+        <v>0.068162</v>
+      </c>
+      <c r="I278" s="5" t="n">
+        <v>0.033031</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -31074,37 +30966,35 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E279" s="5" t="n">
-        <v>0.021565</v>
-      </c>
-      <c r="F279" s="5" t="n">
-        <v>0.025613</v>
-      </c>
-      <c r="G279" s="5" t="n">
-        <v>0.036142</v>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rent and office costs</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H279" s="5" t="n">
+        <v>0.038591</v>
+      </c>
+      <c r="I279" s="5" t="n">
+        <v>0.02901</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -31160,35 +31050,41 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Project investigation</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F280" s="5" t="n">
-        <v>0.021806</v>
-      </c>
-      <c r="G280" s="5" t="n">
-        <v>0.06838</v>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I280" s="5" t="n">
+        <v>0.01816</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -31244,33 +31140,35 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Shareholder information</t>
+          <t>Accounting and legal</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
-      <c r="E281" s="5" t="n">
-        <v>0.000495</v>
-      </c>
-      <c r="F281" s="5" t="n">
-        <v>0.001547</v>
-      </c>
-      <c r="G281" s="5" t="n">
-        <v>0.002941</v>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H281" s="5" t="n">
+        <v>0.023799</v>
+      </c>
+      <c r="I281" s="5" t="n">
+        <v>0.015087</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -31326,15 +31224,19 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -31345,18 +31247,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G282" s="5" t="n">
-        <v>0.010362</v>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H282" s="5" t="n">
+        <v>0.00072</v>
+      </c>
+      <c r="I282" s="5" t="n">
+        <v>0.001557</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -31410,29 +31310,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Transfer agent, listing and filing fees</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>MINERAL PROPERTY EXPENDITURES (Note 5) $</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
       <c r="E283" s="5" t="n">
-        <v>0.016518</v>
+        <v>0.000817</v>
       </c>
       <c r="F283" s="5" t="n">
-        <v>0.015358</v>
+        <v>0.013095</v>
       </c>
       <c r="G283" s="5" t="n">
-        <v>0.037494</v>
+        <v>0.239203</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -31503,22 +31395,18 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Office and sundry</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
       <c r="E284" s="5" t="n">
-        <v>0.08721</v>
+        <v>0.000382</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>0.113649</v>
+        <v>0.001325</v>
       </c>
       <c r="G284" s="5" t="n">
-        <v>0.206022</v>
+        <v>0.002703</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -31589,22 +31477,18 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Office facilities and administrative services</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
       <c r="E285" s="5" t="n">
-        <v>-0.08802699999999999</v>
+        <v>0.048</v>
       </c>
       <c r="F285" s="5" t="n">
-        <v>-0.126744</v>
+        <v>0.048</v>
       </c>
       <c r="G285" s="5" t="n">
-        <v>-0.445225</v>
+        <v>0.048</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -31670,27 +31554,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E286" s="5" t="n">
-        <v>0.0065</v>
+        <v>0.021565</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.000248</v>
+        <v>0.025613</v>
       </c>
       <c r="G286" s="5" t="n">
-        <v>0.010774</v>
+        <v>0.036142</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -31756,29 +31640,25 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E287" s="5" t="n">
-        <v>-9.899999999999999e-05</v>
+          <t>Project investigation</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F287" s="5" t="n">
-        <v>-2.7e-05</v>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021806</v>
+      </c>
+      <c r="G287" s="5" t="n">
+        <v>0.06838</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -31844,23 +31724,23 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>OTHER ITEMS total</t>
+          <t>Shareholder information</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
       <c r="E288" s="5" t="n">
-        <v>0.006401</v>
+        <v>0.000495</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.000221</v>
+        <v>0.001547</v>
       </c>
       <c r="G288" s="5" t="n">
-        <v>0.010774</v>
+        <v>0.002941</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -31926,27 +31806,27 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E289" s="5" t="n">
-        <v>-0.081626</v>
-      </c>
-      <c r="F289" s="5" t="n">
-        <v>-0.126523</v>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>-0.434451</v>
+        <v>0.010362</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -32012,23 +31892,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Deficit, beginning of year</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
+          <t>Transfer agent, listing and filing fees</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E290" s="5" t="n">
-        <v>-0.699443</v>
+        <v>0.016518</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>-0.781069</v>
+        <v>0.015358</v>
       </c>
       <c r="G290" s="5" t="n">
-        <v>-0.907592</v>
+        <v>0.037494</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -32094,23 +31978,27 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Deficit, end of year $</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E291" s="5" t="n">
-        <v>-0.781069</v>
+        <v>0.08721</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>-0.907592</v>
+        <v>0.113649</v>
       </c>
       <c r="G291" s="5" t="n">
-        <v>-1.342043</v>
+        <v>0.206022</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -32176,27 +32064,27 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Loss before other items</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E292" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-0.08802699999999999</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.126744</v>
       </c>
       <c r="G292" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-0.445225</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -32267,22 +32155,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E293" s="5" t="n">
-        <v>5.2001</v>
+        <v>0.0065</v>
       </c>
       <c r="F293" s="5" t="n">
-        <v>12.494994</v>
+        <v>0.000248</v>
       </c>
       <c r="G293" s="5" t="n">
-        <v>21.063929</v>
+        <v>0.010774</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -32348,83 +32236,675 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="n">
+        <v>-9.899999999999999e-05</v>
+      </c>
+      <c r="F294" s="5" t="n">
+        <v>-2.7e-05</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS total</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" s="5" t="n">
+        <v>0.006401</v>
+      </c>
+      <c r="F295" s="5" t="n">
+        <v>0.000221</v>
+      </c>
+      <c r="G295" s="5" t="n">
+        <v>0.010774</v>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="n">
+        <v>-0.081626</v>
+      </c>
+      <c r="F296" s="5" t="n">
+        <v>-0.126523</v>
+      </c>
+      <c r="G296" s="5" t="n">
+        <v>-0.434451</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" s="5" t="n">
+        <v>-0.699443</v>
+      </c>
+      <c r="F297" s="5" t="n">
+        <v>-0.781069</v>
+      </c>
+      <c r="G297" s="5" t="n">
+        <v>-0.907592</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Deficit, end of year $</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" s="5" t="n">
+        <v>-0.781069</v>
+      </c>
+      <c r="F298" s="5" t="n">
+        <v>-0.907592</v>
+      </c>
+      <c r="G298" s="5" t="n">
+        <v>-1.342043</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="F299" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G299" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="n">
+        <v>5.2001</v>
+      </c>
+      <c r="F300" s="5" t="n">
+        <v>12.494994</v>
+      </c>
+      <c r="G300" s="5" t="n">
+        <v>21.063929</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
           <t>EXPENSES</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr">
+      <c r="C301" t="inlineStr">
         <is>
           <t>Consulting</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr">
+      <c r="D301" t="inlineStr">
         <is>
           <t>OtherOperatingExpenses</t>
         </is>
       </c>
-      <c r="E294" s="5" t="n">
+      <c r="E301" s="5" t="n">
         <v>0.00025</v>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R294" t="inlineStr">
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
         <is>
           <t>-</t>
         </is>
